--- a/artfynd/A 57661-2025 artfynd.xlsx
+++ b/artfynd/A 57661-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111541559</v>
+        <v>111541567</v>
       </c>
       <c r="B2" t="n">
-        <v>73696</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442841.3095208929</v>
+        <v>442884</v>
       </c>
       <c r="R2" t="n">
-        <v>6753907.140458568</v>
+        <v>6753905</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -748,19 +743,9 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111541696</v>
+        <v>111541568</v>
       </c>
       <c r="B3" t="n">
-        <v>77186</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442618.8408340383</v>
+        <v>442871</v>
       </c>
       <c r="R3" t="n">
-        <v>6753798.352792068</v>
+        <v>6753908</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -860,19 +840,9 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111541656</v>
+        <v>111541693</v>
       </c>
       <c r="B4" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442619.8621595366</v>
+        <v>442626</v>
       </c>
       <c r="R4" t="n">
-        <v>6753801.25509781</v>
+        <v>6753814</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -972,19 +937,9 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111541657</v>
+        <v>111541694</v>
       </c>
       <c r="B5" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>442576.454087059</v>
+        <v>442642</v>
       </c>
       <c r="R5" t="n">
-        <v>6753828.711480335</v>
+        <v>6753800</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1084,19 +1034,9 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111541560</v>
+        <v>111541695</v>
       </c>
       <c r="B6" t="n">
-        <v>73696</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>442831.6636110337</v>
+        <v>442654</v>
       </c>
       <c r="R6" t="n">
-        <v>6753882.973015812</v>
+        <v>6753797</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1196,19 +1131,9 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111541693</v>
+        <v>111541696</v>
       </c>
       <c r="B7" t="n">
-        <v>77186</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>442625.9194370487</v>
+        <v>442619</v>
       </c>
       <c r="R7" t="n">
-        <v>6753814.291862695</v>
+        <v>6753798</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1308,19 +1228,9 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111541659</v>
+        <v>111541697</v>
       </c>
       <c r="B8" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>442829.6739157947</v>
+        <v>442577</v>
       </c>
       <c r="R8" t="n">
-        <v>6753910.73271188</v>
+        <v>6753840</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1420,19 +1325,9 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,59 +1354,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111541710</v>
+        <v>111559614</v>
       </c>
       <c r="B9" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stamsmyren, Venjan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442842.4557461102</v>
+        <v>442906</v>
       </c>
       <c r="R9" t="n">
-        <v>6753917.823898755</v>
+        <v>6753943</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1541,28 +1422,17 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1581,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111541561</v>
+        <v>111541594</v>
       </c>
       <c r="B10" t="n">
-        <v>73696</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1621,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442841.6167685112</v>
+        <v>442606</v>
       </c>
       <c r="R10" t="n">
-        <v>6753895.947165031</v>
+        <v>6753877</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1654,19 +1519,9 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111541574</v>
+        <v>111541655</v>
       </c>
       <c r="B11" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1733,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442748.2409828438</v>
+        <v>442828</v>
       </c>
       <c r="R11" t="n">
-        <v>6753936.852103127</v>
+        <v>6753892</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1766,19 +1616,9 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,59 +1645,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111541623</v>
+        <v>111541656</v>
       </c>
       <c r="B12" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stamsmyren, Venjan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442802.3768863342</v>
+        <v>442620</v>
       </c>
       <c r="R12" t="n">
-        <v>6753849.392256664</v>
+        <v>6753801</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1887,28 +1713,17 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1927,19 +1742,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111541660</v>
+        <v>111541657</v>
       </c>
       <c r="B13" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1967,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442844.6722924172</v>
+        <v>442577</v>
       </c>
       <c r="R13" t="n">
-        <v>6753904.167692418</v>
+        <v>6753828</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2000,19 +1810,9 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2042,16 +1842,11 @@
         <v>111541658</v>
       </c>
       <c r="B14" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2079,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442809.6324991018</v>
+        <v>442809</v>
       </c>
       <c r="R14" t="n">
-        <v>6753906.677038478</v>
+        <v>6753906</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2112,19 +1907,9 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2151,37 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111541697</v>
+        <v>111541659</v>
       </c>
       <c r="B15" t="n">
-        <v>77186</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2191,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442577.6089857765</v>
+        <v>442829</v>
       </c>
       <c r="R15" t="n">
-        <v>6753839.88142032</v>
+        <v>6753911</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2224,19 +2004,9 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2263,59 +2033,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111541624</v>
+        <v>111541660</v>
       </c>
       <c r="B16" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stamsmyren, Venjan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>442719.924028666</v>
+        <v>442844</v>
       </c>
       <c r="R16" t="n">
-        <v>6753812.289490802</v>
+        <v>6753904</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2345,28 +2101,17 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2385,37 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111541568</v>
+        <v>111541661</v>
       </c>
       <c r="B17" t="n">
-        <v>94134</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2425,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442871.5330500021</v>
+        <v>442850</v>
       </c>
       <c r="R17" t="n">
-        <v>6753908.113967704</v>
+        <v>6753897</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2458,19 +2198,9 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2497,15 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111541594</v>
+        <v>111541559</v>
       </c>
       <c r="B18" t="n">
-        <v>89425</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2513,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2537,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442605.9787055243</v>
+        <v>442842</v>
       </c>
       <c r="R18" t="n">
-        <v>6753876.880489825</v>
+        <v>6753907</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2570,19 +2295,9 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2609,15 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>111541661</v>
+        <v>111541560</v>
       </c>
       <c r="B19" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2625,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2649,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442849.4259995273</v>
+        <v>442832</v>
       </c>
       <c r="R19" t="n">
-        <v>6753896.794511081</v>
+        <v>6753883</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2682,19 +2392,9 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2721,15 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>111541655</v>
+        <v>111541561</v>
       </c>
       <c r="B20" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2737,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2761,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>442827.9075863644</v>
+        <v>442841</v>
       </c>
       <c r="R20" t="n">
-        <v>6753891.789559421</v>
+        <v>6753896</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2794,19 +2489,9 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2833,15 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111541695</v>
+        <v>111559602</v>
       </c>
       <c r="B21" t="n">
-        <v>77186</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2849,21 +2529,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2873,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>442653.8972917829</v>
+        <v>442877</v>
       </c>
       <c r="R21" t="n">
-        <v>6753796.814187178</v>
+        <v>6753979</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2906,19 +2586,9 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2945,15 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111541567</v>
+        <v>111541572</v>
       </c>
       <c r="B22" t="n">
-        <v>94134</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2961,21 +2626,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2985,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>442884.6456257988</v>
+        <v>442636</v>
       </c>
       <c r="R22" t="n">
-        <v>6753905.471018846</v>
+        <v>6753787</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3018,19 +2683,9 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3057,15 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>111541572</v>
+        <v>111541573</v>
       </c>
       <c r="B23" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3097,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>442636.1885649032</v>
+        <v>442603</v>
       </c>
       <c r="R23" t="n">
-        <v>6753786.397638152</v>
+        <v>6753803</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3130,19 +2780,9 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3169,15 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>111541694</v>
+        <v>111541574</v>
       </c>
       <c r="B24" t="n">
-        <v>77186</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3185,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3209,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>442641.7586931501</v>
+        <v>442748</v>
       </c>
       <c r="R24" t="n">
-        <v>6753799.442343741</v>
+        <v>6753937</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3242,19 +2877,9 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3281,15 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111559602</v>
+        <v>111559606</v>
       </c>
       <c r="B25" t="n">
-        <v>73696</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3297,21 +2917,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3321,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>442876.578627035</v>
+        <v>442828</v>
       </c>
       <c r="R25" t="n">
-        <v>6753979.54018424</v>
+        <v>6754012</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3354,19 +2974,9 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3393,50 +3003,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>111559606</v>
+        <v>111541710</v>
       </c>
       <c r="B26" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stamsmyren, Venjan, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>442828.3782149812</v>
+        <v>442842</v>
       </c>
       <c r="R26" t="n">
-        <v>6754011.933498133</v>
+        <v>6753918</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3466,27 +3080,18 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3505,15 +3110,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>111559614</v>
+        <v>111541622</v>
       </c>
       <c r="B27" t="n">
-        <v>90678</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3521,34 +3121,43 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4366</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stamsmyren, Venjan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>442906.1922857394</v>
+        <v>442495</v>
       </c>
       <c r="R27" t="n">
-        <v>6753942.581297852</v>
+        <v>6753943</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3578,27 +3187,18 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3614,6 +3214,414 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>111541623</v>
+      </c>
+      <c r="B28" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stamsmyren, Venjan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>442802</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6753850</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>111541624</v>
+      </c>
+      <c r="B29" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Stamsmyren, Venjan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>442720</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6753813</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>111559624</v>
+      </c>
+      <c r="B30" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Stamsmyren, Venjan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>442514</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6753962</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>111559625</v>
+      </c>
+      <c r="B31" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Stamsmyren, Venjan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>442464</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6754013</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57661-2025 artfynd.xlsx
+++ b/artfynd/A 57661-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541693</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541694</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541695</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541696</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541697</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541594</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541656</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541657</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541572</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541573</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1749,6 +1804,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541622</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1846,6 +1906,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559624</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1943,6 +2008,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559625</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2040,6 +2110,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541567</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2137,6 +2212,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541568</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2234,6 +2314,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559614</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2331,6 +2416,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541655</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2428,6 +2518,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541658</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2525,6 +2620,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541659</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2622,6 +2722,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541660</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2719,6 +2824,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541661</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2816,6 +2926,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541559</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2913,6 +3028,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541560</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3010,6 +3130,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541561</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3107,6 +3232,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559602</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3204,6 +3334,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541574</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3301,6 +3436,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111559606</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3408,6 +3548,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541710</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3515,6 +3660,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541623</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3622,8 +3772,45 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541624</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>